--- a/queens-multifamily.xlsx
+++ b/queens-multifamily.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29912"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30006"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D782C271-E776-4A4D-8043-F8F3262F05A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E73D5010-A601-4D85-9D65-2D5B8EEB0A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -474,7 +474,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -511,8 +511,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -575,11 +581,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -666,11 +681,12 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="7" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="4" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="4" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -983,6 +999,31 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{5D6D7179-286F-4F0B-A285-04C356932F9F}">
+  <we:reference id="WA200009404" version="1.0.0.8" store="en-us" storeType="omex"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="en-us" storeType="omex"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:G50"/>
@@ -2876,7 +2917,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E3B29E6-1005-4680-9EB6-693825532BFC}">
-  <dimension ref="B1:K7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="12" style="4" customWidth="1"/>
@@ -2885,85 +2926,158 @@
     <col min="8" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11">
+    <row r="1" spans="1:11">
       <c r="C1" s="53" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="2" spans="2:11">
-      <c r="B2" s="58">
+    <row r="2" spans="1:11">
+      <c r="A2" s="59"/>
+      <c r="B2" s="57">
         <f>' Returns'!C35</f>
         <v>6.1550804972648629E-2</v>
       </c>
       <c r="C2" s="50">
         <v>4.2500000000000003E-2</v>
       </c>
-      <c r="D2" s="55">
+      <c r="D2" s="54">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="E2" s="55">
+      <c r="E2" s="54">
         <v>4.7500000000000001E-2</v>
       </c>
-      <c r="F2" s="55">
+      <c r="F2" s="54">
         <v>0.05</v>
       </c>
-      <c r="G2" s="55">
+      <c r="G2" s="54">
         <v>5.2499999999999998E-2</v>
       </c>
       <c r="K2" s="15"/>
     </row>
-    <row r="3" spans="2:11">
-      <c r="B3" s="56" t="s">
+    <row r="3" spans="1:11">
+      <c r="B3" s="55" t="s">
         <v>113</v>
       </c>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-    </row>
-    <row r="4" spans="2:11">
+      <c r="C3" s="56">
+        <f>XIRR(CHOOSE({1,2,3,4,5,6,7,8},' Returns'!$C$14,' Returns'!$D$14,' Returns'!$E$14,'Pro Forma'!$B$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$B$12,'Pro Forma'!$C$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$C$12,'Pro Forma'!$D$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$D$12,'Pro Forma'!$E$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$E$12,('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)+('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)/C$2*(1-'Assumptions Dashboard'!$C$50)),' Returns'!$C$29:$J$29)</f>
+        <v>4.6067336201667794E-2</v>
+      </c>
+      <c r="D3" s="56">
+        <f>XIRR(CHOOSE({1,2,3,4,5,6,7,8},' Returns'!$C$14,' Returns'!$D$14,' Returns'!$E$14,'Pro Forma'!$B$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$B$12,'Pro Forma'!$C$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$C$12,'Pro Forma'!$D$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$D$12,'Pro Forma'!$E$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$E$12,('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)+('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)/D$2*(1-'Assumptions Dashboard'!$C$50)),' Returns'!$C$29:$J$29)</f>
+        <v>3.7489923834800723E-2</v>
+      </c>
+      <c r="E3" s="56">
+        <f>XIRR(CHOOSE({1,2,3,4,5,6,7,8},' Returns'!$C$14,' Returns'!$D$14,' Returns'!$E$14,'Pro Forma'!$B$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$B$12,'Pro Forma'!$C$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$C$12,'Pro Forma'!$D$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$D$12,'Pro Forma'!$E$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$E$12,('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)+('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)/E$2*(1-'Assumptions Dashboard'!$C$50)),' Returns'!$C$29:$J$29)</f>
+        <v>2.9478934407234193E-2</v>
+      </c>
+      <c r="F3" s="56">
+        <f>XIRR(CHOOSE({1,2,3,4,5,6,7,8},' Returns'!$C$14,' Returns'!$D$14,' Returns'!$E$14,'Pro Forma'!$B$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$B$12,'Pro Forma'!$C$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$C$12,'Pro Forma'!$D$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$D$12,'Pro Forma'!$E$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$E$12,('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)+('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)/F$2*(1-'Assumptions Dashboard'!$C$50)),' Returns'!$C$29:$J$29)</f>
+        <v>2.1971419453620914E-2</v>
+      </c>
+      <c r="G3" s="56">
+        <f>XIRR(CHOOSE({1,2,3,4,5,6,7,8},' Returns'!$C$14,' Returns'!$D$14,' Returns'!$E$14,'Pro Forma'!$B$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$B$12,'Pro Forma'!$C$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$C$12,'Pro Forma'!$D$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$D$12,'Pro Forma'!$E$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$E$12,('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)+('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)/G$2*(1-'Assumptions Dashboard'!$C$50)),' Returns'!$C$29:$J$29)</f>
+        <v>1.491410434246063E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="B4" s="51" t="s">
         <v>114</v>
       </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-    </row>
-    <row r="5" spans="2:11">
-      <c r="B5" s="56" t="s">
+      <c r="C4" s="56">
+        <f>XIRR(CHOOSE({1,2,3,4,5,6,7,8},' Returns'!$C$14,' Returns'!$D$14,' Returns'!$E$14,'Pro Forma'!$B$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$B$12,'Pro Forma'!$C$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$C$12,'Pro Forma'!$D$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$D$12,'Pro Forma'!$E$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$E$12,('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)+('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)/C$2*(1-'Assumptions Dashboard'!$C$50)),' Returns'!$C$29:$J$29)</f>
+        <v>6.2836447358131417E-2</v>
+      </c>
+      <c r="D4" s="56">
+        <f>XIRR(CHOOSE({1,2,3,4,5,6,7,8},' Returns'!$C$14,' Returns'!$D$14,' Returns'!$E$14,'Pro Forma'!$B$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$B$12,'Pro Forma'!$C$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$C$12,'Pro Forma'!$D$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$D$12,'Pro Forma'!$E$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$E$12,('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)+('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)/D$2*(1-'Assumptions Dashboard'!$C$50)),' Returns'!$C$29:$J$29)</f>
+        <v>5.4169622063636777E-2</v>
+      </c>
+      <c r="E4" s="56">
+        <f>XIRR(CHOOSE({1,2,3,4,5,6,7,8},' Returns'!$C$14,' Returns'!$D$14,' Returns'!$E$14,'Pro Forma'!$B$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$B$12,'Pro Forma'!$C$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$C$12,'Pro Forma'!$D$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$D$12,'Pro Forma'!$E$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$E$12,('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)+('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)/E$2*(1-'Assumptions Dashboard'!$C$50)),' Returns'!$C$29:$J$29)</f>
+        <v>4.6075680851936349E-2</v>
+      </c>
+      <c r="F4" s="56">
+        <f>XIRR(CHOOSE({1,2,3,4,5,6,7,8},' Returns'!$C$14,' Returns'!$D$14,' Returns'!$E$14,'Pro Forma'!$B$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$B$12,'Pro Forma'!$C$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$C$12,'Pro Forma'!$D$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$D$12,'Pro Forma'!$E$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$E$12,('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)+('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)/F$2*(1-'Assumptions Dashboard'!$C$50)),' Returns'!$C$29:$J$29)</f>
+        <v>3.8490942120552069E-2</v>
+      </c>
+      <c r="G4" s="56">
+        <f>XIRR(CHOOSE({1,2,3,4,5,6,7,8},' Returns'!$C$14,' Returns'!$D$14,' Returns'!$E$14,'Pro Forma'!$B$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$B$12,'Pro Forma'!$C$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$C$12,'Pro Forma'!$D$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$D$12,'Pro Forma'!$E$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$E$12,('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)+('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)/G$2*(1-'Assumptions Dashboard'!$C$50)),' Returns'!$C$29:$J$29)</f>
+        <v>3.1361511349678031E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="B5" s="55" t="s">
         <v>115</v>
       </c>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="57">
-        <f>' Returns'!C35</f>
+      <c r="C5" s="56">
+        <f>XIRR(CHOOSE({1,2,3,4,5,6,7,8},' Returns'!$C$14,' Returns'!$D$14,' Returns'!$E$14,'Pro Forma'!$B$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$B$12,'Pro Forma'!$C$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$C$12,'Pro Forma'!$D$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$D$12,'Pro Forma'!$E$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$E$12,('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)+('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)/C$2*(1-'Assumptions Dashboard'!$C$50)),' Returns'!$C$29:$J$29)</f>
+        <v>7.846929132938385E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <f>XIRR(CHOOSE({1,2,3,4,5,6,7,8},' Returns'!$C$14,' Returns'!$D$14,' Returns'!$E$14,'Pro Forma'!$B$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$B$12,'Pro Forma'!$C$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$C$12,'Pro Forma'!$D$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$D$12,'Pro Forma'!$E$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$E$12,('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)+('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)/D$2*(1-'Assumptions Dashboard'!$C$50)),' Returns'!$C$29:$J$29)</f>
+        <v>6.9720628857612613E-2</v>
+      </c>
+      <c r="E5" s="58">
+        <f>XIRR(CHOOSE({1,2,3,4,5,6,7,8},' Returns'!$C$14,' Returns'!$D$14,' Returns'!$E$14,'Pro Forma'!$B$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$B$12,'Pro Forma'!$C$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$C$12,'Pro Forma'!$D$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$D$12,'Pro Forma'!$E$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$E$12,('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)+('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)/E$2*(1-'Assumptions Dashboard'!$C$50)),' Returns'!$C$29:$J$29)</f>
         <v>6.1550804972648629E-2</v>
       </c>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-    </row>
-    <row r="6" spans="2:11">
+      <c r="F5" s="56">
+        <f>XIRR(CHOOSE({1,2,3,4,5,6,7,8},' Returns'!$C$14,' Returns'!$D$14,' Returns'!$E$14,'Pro Forma'!$B$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$B$12,'Pro Forma'!$C$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$C$12,'Pro Forma'!$D$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$D$12,'Pro Forma'!$E$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$E$12,('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)+('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)/F$2*(1-'Assumptions Dashboard'!$C$50)),' Returns'!$C$29:$J$29)</f>
+        <v>5.3895458579063416E-2</v>
+      </c>
+      <c r="G5" s="56">
+        <f>XIRR(CHOOSE({1,2,3,4,5,6,7,8},' Returns'!$C$14,' Returns'!$D$14,' Returns'!$E$14,'Pro Forma'!$B$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$B$12,'Pro Forma'!$C$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$C$12,'Pro Forma'!$D$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$D$12,'Pro Forma'!$E$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$E$12,('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)+('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)/G$2*(1-'Assumptions Dashboard'!$C$50)),' Returns'!$C$29:$J$29)</f>
+        <v>4.6700122952461232E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="B6" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-    </row>
-    <row r="7" spans="2:11">
+      <c r="C6" s="56">
+        <f>XIRR(CHOOSE({1,2,3,4,5,6,7,8},' Returns'!$C$14,' Returns'!$D$14,' Returns'!$E$14,'Pro Forma'!$B$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$B$12,'Pro Forma'!$C$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$C$12,'Pro Forma'!$D$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$D$12,'Pro Forma'!$E$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$E$12,('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)+('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)/C$2*(1-'Assumptions Dashboard'!$C$50)),' Returns'!$C$29:$J$29)</f>
+        <v>9.3125882744789126E-2</v>
+      </c>
+      <c r="D6" s="56">
+        <f>XIRR(CHOOSE({1,2,3,4,5,6,7,8},' Returns'!$C$14,' Returns'!$D$14,' Returns'!$E$14,'Pro Forma'!$B$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$B$12,'Pro Forma'!$C$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$C$12,'Pro Forma'!$D$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$D$12,'Pro Forma'!$E$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$E$12,('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)+('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)/D$2*(1-'Assumptions Dashboard'!$C$50)),' Returns'!$C$29:$J$29)</f>
+        <v>8.4301838278770469E-2</v>
+      </c>
+      <c r="E6" s="56">
+        <f>XIRR(CHOOSE({1,2,3,4,5,6,7,8},' Returns'!$C$14,' Returns'!$D$14,' Returns'!$E$14,'Pro Forma'!$B$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$B$12,'Pro Forma'!$C$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$C$12,'Pro Forma'!$D$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$D$12,'Pro Forma'!$E$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$E$12,('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)+('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)/E$2*(1-'Assumptions Dashboard'!$C$50)),' Returns'!$C$29:$J$29)</f>
+        <v>7.60621577501297E-2</v>
+      </c>
+      <c r="F6" s="56">
+        <f>XIRR(CHOOSE({1,2,3,4,5,6,7,8},' Returns'!$C$14,' Returns'!$D$14,' Returns'!$E$14,'Pro Forma'!$B$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$B$12,'Pro Forma'!$C$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$C$12,'Pro Forma'!$D$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$D$12,'Pro Forma'!$E$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$E$12,('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)+('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)/F$2*(1-'Assumptions Dashboard'!$C$50)),' Returns'!$C$29:$J$29)</f>
+        <v>6.8341842293739311E-2</v>
+      </c>
+      <c r="G6" s="56">
+        <f>XIRR(CHOOSE({1,2,3,4,5,6,7,8},' Returns'!$C$14,' Returns'!$D$14,' Returns'!$E$14,'Pro Forma'!$B$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$B$12,'Pro Forma'!$C$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$C$12,'Pro Forma'!$D$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$D$12,'Pro Forma'!$E$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$E$12,('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)+('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)/G$2*(1-'Assumptions Dashboard'!$C$50)),' Returns'!$C$29:$J$29)</f>
+        <v>6.1085888743400568E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="B7" s="52" t="s">
         <v>117</v>
       </c>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
+      <c r="C7" s="56">
+        <f>XIRR(CHOOSE({1,2,3,4,5,6,7,8},' Returns'!$C$14,' Returns'!$D$14,' Returns'!$E$14,'Pro Forma'!$B$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$B$12,'Pro Forma'!$C$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$C$12,'Pro Forma'!$D$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$D$12,'Pro Forma'!$E$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$E$12,('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)+('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)/C$2*(1-'Assumptions Dashboard'!$C$50)),' Returns'!$C$29:$J$29)</f>
+        <v>0.10693387389183043</v>
+      </c>
+      <c r="D7" s="56">
+        <f>XIRR(CHOOSE({1,2,3,4,5,6,7,8},' Returns'!$C$14,' Returns'!$D$14,' Returns'!$E$14,'Pro Forma'!$B$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$B$12,'Pro Forma'!$C$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$C$12,'Pro Forma'!$D$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$D$12,'Pro Forma'!$E$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$E$12,('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)+('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)/D$2*(1-'Assumptions Dashboard'!$C$50)),' Returns'!$C$29:$J$29)</f>
+        <v>9.8040014505386353E-2</v>
+      </c>
+      <c r="E7" s="56">
+        <f>XIRR(CHOOSE({1,2,3,4,5,6,7,8},' Returns'!$C$14,' Returns'!$D$14,' Returns'!$E$14,'Pro Forma'!$B$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$B$12,'Pro Forma'!$C$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$C$12,'Pro Forma'!$D$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$D$12,'Pro Forma'!$E$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$E$12,('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)+('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)/E$2*(1-'Assumptions Dashboard'!$C$50)),' Returns'!$C$29:$J$29)</f>
+        <v>8.973566591739654E-2</v>
+      </c>
+      <c r="F7" s="56">
+        <f>XIRR(CHOOSE({1,2,3,4,5,6,7,8},' Returns'!$C$14,' Returns'!$D$14,' Returns'!$E$14,'Pro Forma'!$B$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$B$12,'Pro Forma'!$C$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$C$12,'Pro Forma'!$D$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$D$12,'Pro Forma'!$E$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$E$12,('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)+('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)/F$2*(1-'Assumptions Dashboard'!$C$50)),' Returns'!$C$29:$J$29)</f>
+        <v>8.1955239176750197E-2</v>
+      </c>
+      <c r="G7" s="56">
+        <f>XIRR(CHOOSE({1,2,3,4,5,6,7,8},' Returns'!$C$14,' Returns'!$D$14,' Returns'!$E$14,'Pro Forma'!$B$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$B$12,'Pro Forma'!$C$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$C$12,'Pro Forma'!$D$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$D$12,'Pro Forma'!$E$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$E$12,('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)+('Pro Forma'!$F$5*(1+(ROW()-5)*0.05)-'Pro Forma'!$F$12)/G$2*(1-'Assumptions Dashboard'!$C$50)),' Returns'!$C$29:$J$29)</f>
+        <v>7.4643227458000186E-2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
